--- a/분석 결과/kenya_macro_history.xlsx
+++ b/분석 결과/kenya_macro_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,21 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>129.491871</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/분석 결과/kenya_macro_history.xlsx
+++ b/분석 결과/kenya_macro_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,6 +485,21 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>129.216109</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/분석 결과/kenya_macro_history.xlsx
+++ b/분석 결과/kenya_macro_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,6 +500,21 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>129.387462</v>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/분석 결과/kenya_macro_history.xlsx
+++ b/분석 결과/kenya_macro_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,6 +515,21 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>129.404185</v>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
